--- a/Project gestion/Planned budget/Dépenses.xlsx
+++ b/Project gestion/Planned budget/Dépenses.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thibm\OneDrive\Documents\GitHub\CFR2027\Project gestion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thibm\OneDrive\Documents\GitHub\CFR2027\Project gestion\Planned budget\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBA64AF-67D1-44CD-99A8-0F537E93028D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97460566-4F73-4DA2-B96C-7F8F04B35BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="3" xr2:uid="{DC506655-D796-47EE-BDAC-EDB6EB12EC7A}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="87">
   <si>
     <t>Produit</t>
   </si>
@@ -279,6 +279,18 @@
   </si>
   <si>
     <t>370C-22155</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Diamètre d'entrée (mm)</t>
+  </si>
+  <si>
+    <t>Compatibilité avec LN298N</t>
+  </si>
+  <si>
+    <t>Référence</t>
   </si>
 </sst>
 </file>
@@ -351,7 +363,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -814,98 +826,61 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -913,7 +888,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1002,35 +977,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1867,17 +1837,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B7EAC6-6B63-41E7-8C21-49F258C20125}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.77734375" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" customWidth="1"/>
     <col min="6" max="6" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.88671875" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.109375" style="14"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -1886,7 +1857,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="D2" s="40" t="s">
         <v>42</v>
@@ -1907,12 +1878,12 @@
         <v>47</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="44" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1920,38 +1891,37 @@
       <c r="A3" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="55">
+      <c r="D3" s="53">
         <v>6</v>
       </c>
-      <c r="E3" s="55">
+      <c r="E3" s="53">
         <v>3.6</v>
       </c>
-      <c r="F3" s="55">
+      <c r="F3" s="53">
         <v>2.7</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="55">
+      <c r="H3" s="53">
         <v>300</v>
       </c>
-      <c r="I3" s="56">
+      <c r="I3" s="54">
         <v>21.5</v>
       </c>
-      <c r="J3" s="57" t="s">
+      <c r="J3" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="58"/>
-      <c r="L3" s="66">
-        <v>8</v>
-      </c>
-      <c r="M3" s="65" t="s">
+      <c r="L3" s="62">
+        <v>10</v>
+      </c>
+      <c r="M3" s="64" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1986,10 +1956,10 @@
       <c r="J4" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="63">
+      <c r="L4" s="45">
         <v>5</v>
       </c>
-      <c r="M4" s="61" t="s">
+      <c r="M4" s="46" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2024,10 +1994,10 @@
       <c r="J5" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="63">
+      <c r="L5" s="45">
         <v>0</v>
       </c>
-      <c r="M5" s="61" t="s">
+      <c r="M5" s="46" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2062,10 +2032,10 @@
       <c r="J6" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="45">
         <v>0</v>
       </c>
-      <c r="M6" s="61" t="s">
+      <c r="M6" s="46" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2100,10 +2070,10 @@
       <c r="J7" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="63">
+      <c r="L7" s="45">
         <v>0</v>
       </c>
-      <c r="M7" s="61" t="s">
+      <c r="M7" s="46" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2138,10 +2108,10 @@
       <c r="J8" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="63">
+      <c r="L8" s="45">
         <v>5</v>
       </c>
-      <c r="M8" s="61" t="s">
+      <c r="M8" s="46" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2152,7 +2122,7 @@
       <c r="B9" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="68">
+      <c r="C9" s="58">
         <v>4755</v>
       </c>
       <c r="D9" s="28">
@@ -2176,10 +2146,10 @@
       <c r="J9" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="L9" s="63">
+      <c r="L9" s="45">
         <v>0</v>
       </c>
-      <c r="M9" s="61" t="s">
+      <c r="M9" s="46" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2214,10 +2184,10 @@
       <c r="J10" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L10" s="63">
-        <v>10</v>
-      </c>
-      <c r="M10" s="61" t="s">
+      <c r="L10" s="45">
+        <v>8</v>
+      </c>
+      <c r="M10" s="46" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2252,10 +2222,10 @@
       <c r="J11" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="L11" s="64">
+      <c r="L11" s="47">
         <v>8</v>
       </c>
-      <c r="M11" s="62" t="s">
+      <c r="M11" s="49" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2264,8 +2234,8 @@
       <c r="B14" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="44" t="s">
-        <v>23</v>
+      <c r="C14" s="40" t="s">
+        <v>86</v>
       </c>
       <c r="D14" s="44" t="s">
         <v>42</v>
@@ -2279,7 +2249,7 @@
       <c r="G14" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="H14" s="67" t="s">
+      <c r="H14" s="57" t="s">
         <v>47</v>
       </c>
       <c r="I14"/>
@@ -2294,38 +2264,38 @@
       <c r="A15" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="63">
         <v>5</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="63">
         <f>-58</f>
         <v>-58</v>
       </c>
-      <c r="F15" s="74">
+      <c r="F15" s="63">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G15" s="74">
+      <c r="G15" s="63">
         <v>4.3</v>
       </c>
-      <c r="H15" s="75">
+      <c r="H15" s="65">
         <v>6.9</v>
       </c>
       <c r="I15"/>
-      <c r="L15" s="74">
+      <c r="L15" s="62">
         <v>8</v>
       </c>
-      <c r="M15" s="76" t="s">
+      <c r="M15" s="64" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="56" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="45" t="s">
@@ -2346,19 +2316,19 @@
       <c r="G16" s="1">
         <v>4.3</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="66">
         <v>5.19</v>
       </c>
       <c r="I16"/>
-      <c r="L16" s="1">
-        <v>5</v>
+      <c r="L16" s="45">
+        <v>6</v>
       </c>
       <c r="M16" s="46" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="61" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="47" t="s">
@@ -2379,108 +2349,88 @@
       <c r="G17" s="48">
         <v>4.3</v>
       </c>
-      <c r="H17" s="53">
+      <c r="H17" s="67">
         <v>3.69</v>
       </c>
       <c r="I17"/>
-      <c r="L17" s="48">
-        <v>5</v>
+      <c r="L17" s="47">
+        <v>6</v>
       </c>
       <c r="M17" s="49" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="59"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="59"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="H18" s="60"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="59"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
       <c r="E19" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="59"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="59"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="59"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="59"/>
+      <c r="H19" s="60"/>
+    </row>
+    <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H20" s="60"/>
+    </row>
+    <row r="21" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21"/>
+      <c r="L21" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="M21" s="44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="69"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="71"/>
+      <c r="I22"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="64"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="59"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="59"/>
+      <c r="A23" s="68"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="I23"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="46"/>
+    </row>
+    <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="68"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="I24"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="49"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2702,23 +2652,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007934F44BA1E0F24F9930540811A2EDB6" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="63da83260db1d72dc3600b2d6132f719">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2a37fc6c6d9ad226a4d0af2afcddd6e5" ns3:_="">
     <xsd:import namespace="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b"/>
@@ -2868,10 +2801,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E9B7E90-EAE5-48E9-9092-492A01032B48}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2630977E-B0CF-45C9-B99D-25EACCA74DA4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2887,19 +2847,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2630977E-B0CF-45C9-B99D-25EACCA74DA4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E9B7E90-EAE5-48E9-9092-492A01032B48}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="87ca6a5b-3fa2-4330-b2d3-ceb5dc3ac37b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>